--- a/data/trans_dic/P40_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P40_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 15,59</t>
+          <t>9,23; 15,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 14,88</t>
+          <t>8,3; 15,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,16</t>
+          <t>7,04; 13,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,07; 18,05</t>
+          <t>11,42; 17,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,69; 21,18</t>
+          <t>12,31; 20,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 17,62</t>
+          <t>9,49; 17,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 15,31</t>
+          <t>7,74; 14,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,16; 18,51</t>
+          <t>13,74; 19,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 16,37</t>
+          <t>11,16; 16,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,43; 14,56</t>
+          <t>9,39; 14,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,82</t>
+          <t>8,24; 12,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,37; 17,57</t>
+          <t>13,2; 17,47</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 16,53</t>
+          <t>9,12; 16,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 15,77</t>
+          <t>8,85; 15,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 15,29</t>
+          <t>8,22; 14,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 18,16</t>
+          <t>11,29; 17,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 21,6</t>
+          <t>13,23; 20,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 18,87</t>
+          <t>10,68; 18,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,58; 19,46</t>
+          <t>11,37; 19,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 22,01</t>
+          <t>15,28; 21,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,25; 17,17</t>
+          <t>11,91; 17,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 15,71</t>
+          <t>10,59; 15,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,62; 15,76</t>
+          <t>10,72; 15,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,29; 18,88</t>
+          <t>14,13; 18,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,98; 20,43</t>
+          <t>14,25; 20,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,94; 24,76</t>
+          <t>18,01; 24,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 21,68</t>
+          <t>14,89; 21,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 23,58</t>
+          <t>17,61; 24,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 36,63</t>
+          <t>22,33; 36,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 29,28</t>
+          <t>17,95; 28,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,82; 37,6</t>
+          <t>22,22; 38,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,52; 37,56</t>
+          <t>25,14; 36,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,98; 22,85</t>
+          <t>17,18; 22,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,02; 24,96</t>
+          <t>19,1; 24,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 24,56</t>
+          <t>18,0; 24,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 25,53</t>
+          <t>21,08; 26,91</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,33; 21,77</t>
+          <t>17,19; 21,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 24,38</t>
+          <t>19,36; 24,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,8; 20,23</t>
+          <t>15,49; 20,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,62; 24,78</t>
+          <t>19,2; 24,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,28; 27,84</t>
+          <t>21,32; 27,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 24,37</t>
+          <t>18,27; 24,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 23,08</t>
+          <t>17,49; 23,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 24,2</t>
+          <t>21,53; 26,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,44; 23,11</t>
+          <t>19,38; 23,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,65; 23,45</t>
+          <t>19,68; 23,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 20,69</t>
+          <t>17,17; 20,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,85; 23,14</t>
+          <t>20,87; 24,27</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,97; 25,75</t>
+          <t>16,5; 25,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 19,7</t>
+          <t>13,28; 19,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,52; 26,08</t>
+          <t>19,13; 26,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,41; 28,97</t>
+          <t>18,98; 26,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,37; 34,81</t>
+          <t>26,92; 35,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,84; 38,84</t>
+          <t>31,81; 39,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,54; 35,82</t>
+          <t>28,75; 35,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 58,1</t>
+          <t>34,94; 40,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,18; 29,98</t>
+          <t>23,88; 29,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,0; 30,0</t>
+          <t>25,05; 30,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,09; 30,23</t>
+          <t>25,34; 30,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,32; 46,22</t>
+          <t>29,15; 33,64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,29</t>
+          <t>2,43; 7,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,39</t>
+          <t>1,52; 6,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,93</t>
+          <t>3,39; 8,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 13,82</t>
+          <t>4,95; 14,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,61; 39,06</t>
+          <t>33,53; 39,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,16; 36,87</t>
+          <t>31,11; 37,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,18; 34,7</t>
+          <t>28,36; 34,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,94; 36,9</t>
+          <t>30,14; 35,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,7; 32,37</t>
+          <t>27,87; 32,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,71; 30,82</t>
+          <t>25,94; 30,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,33; 28,37</t>
+          <t>23,51; 28,97</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,91; 30,5</t>
+          <t>24,86; 30,28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 17,27</t>
+          <t>14,7; 17,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,59; 18,41</t>
+          <t>15,52; 18,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 17,29</t>
+          <t>14,79; 17,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,04; 19,56</t>
+          <t>17,17; 19,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,95; 30,14</t>
+          <t>27,01; 30,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,4; 28,54</t>
+          <t>25,32; 28,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,56; 26,68</t>
+          <t>23,65; 26,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,35; 31,66</t>
+          <t>26,5; 29,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,31; 23,35</t>
+          <t>21,33; 23,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,97; 23,01</t>
+          <t>20,87; 22,94</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19,68; 21,62</t>
+          <t>19,63; 21,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,04; 25,09</t>
+          <t>22,38; 24,13</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74158</t>
+          <t>78036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>70868</t>
+          <t>79566</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>145025</t>
+          <t>157602</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45401; 73881</t>
+          <t>43752; 72387</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36826; 64182</t>
+          <t>35781; 65168</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31506; 56337</t>
+          <t>30134; 55784</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60964; 91186</t>
+          <t>62891; 94981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38903; 64956</t>
+          <t>37761; 63880</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28799; 55023</t>
+          <t>29633; 53627</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26654; 52679</t>
+          <t>26625; 50996</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58865; 82841</t>
+          <t>67092; 94861</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90274; 127791</t>
+          <t>87082; 127681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70104; 108306</t>
+          <t>69836; 108005</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63938; 98999</t>
+          <t>63619; 100278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>127372; 167402</t>
+          <t>137171; 181520</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66125</t>
+          <t>68474</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70669</t>
+          <t>77211</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>136794</t>
+          <t>145685</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34076; 60502</t>
+          <t>33374; 58751</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36671; 65565</t>
+          <t>36783; 65662</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31191; 57400</t>
+          <t>30846; 56075</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53441; 82108</t>
+          <t>54572; 84001</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50570; 80336</t>
+          <t>49187; 77122</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35910; 63410</t>
+          <t>35872; 63815</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42637; 71684</t>
+          <t>41893; 71158</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59192; 84224</t>
+          <t>64652; 91088</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90424; 126684</t>
+          <t>87857; 126908</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79077; 118111</t>
+          <t>79589; 120063</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78991; 117177</t>
+          <t>79719; 118586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>119291; 157590</t>
+          <t>128058; 167931</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94644</t>
+          <t>100074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52072</t>
+          <t>56830</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>146716</t>
+          <t>156904</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75703; 110586</t>
+          <t>77154; 108874</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>112287; 154959</t>
+          <t>112692; 155778</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78896; 112960</t>
+          <t>77577; 113424</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39203; 157549</t>
+          <t>83028; 116429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37570; 61458</t>
+          <t>37467; 61224</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46675; 75586</t>
+          <t>46344; 73872</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37664; 62059</t>
+          <t>36676; 63190</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44263; 62685</t>
+          <t>47135; 68035</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120391; 162068</t>
+          <t>121848; 162510</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168090; 220597</t>
+          <t>168798; 219051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123787; 168526</t>
+          <t>123515; 167606</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66139; 213244</t>
+          <t>138908; 177393</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229658</t>
+          <t>245601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>180336</t>
+          <t>204034</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>409995</t>
+          <t>449635</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>214440; 269322</t>
+          <t>212752; 267290</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>219130; 278947</t>
+          <t>221495; 280157</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>179863; 230265</t>
+          <t>176393; 230139</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>203052; 256415</t>
+          <t>217296; 274352</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>152014; 198834</t>
+          <t>152297; 196574</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>137825; 185354</t>
+          <t>139001; 184058</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>142388; 189075</t>
+          <t>143264; 190269</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>103888; 236738</t>
+          <t>185391; 225791</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>379440; 450996</t>
+          <t>378279; 449033</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>374269; 446616</t>
+          <t>374833; 449454</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>334772; 405005</t>
+          <t>336078; 408969</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>278740; 465798</t>
+          <t>415997; 483805</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118139</t>
+          <t>126575</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>355163</t>
+          <t>311719</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>473302</t>
+          <t>438294</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>59503; 90266</t>
+          <t>57830; 89230</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67596; 99023</t>
+          <t>66777; 100274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>120126; 160482</t>
+          <t>117701; 161666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101713; 137620</t>
+          <t>107826; 147700</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>155653; 197969</t>
+          <t>153096; 199693</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>241863; 295001</t>
+          <t>241593; 297772</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>209447; 262918</t>
+          <t>210975; 262606</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>302810; 488784</t>
+          <t>290337; 336663</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>222281; 275598</t>
+          <t>219520; 274040</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>315585; 378759</t>
+          <t>316185; 383049</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>338504; 407958</t>
+          <t>341926; 405176</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>412273; 608424</t>
+          <t>407746; 470630</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>257531</t>
+          <t>278490</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>274853</t>
+          <t>298064</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7187; 21749</t>
+          <t>7235; 20942</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3024; 16476</t>
+          <t>3929; 17655</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10195; 25562</t>
+          <t>9695; 25038</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9783; 33242</t>
+          <t>11751; 33567</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>419160; 487076</t>
+          <t>418128; 486467</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>342791; 405610</t>
+          <t>342336; 408909</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>301781; 371627</t>
+          <t>303677; 368421</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>235573; 280971</t>
+          <t>254450; 302463</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>427968; 500215</t>
+          <t>430572; 500453</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>349117; 418497</t>
+          <t>352217; 418304</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>316624; 385013</t>
+          <t>319012; 393204</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>249549; 305595</t>
+          <t>268895; 327456</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600046</t>
+          <t>638334</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>986640</t>
+          <t>1007851</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1586685</t>
+          <t>1646185</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>480178; 564182</t>
+          <t>480297; 562610</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>526604; 621752</t>
+          <t>524061; 620376</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>492973; 581781</t>
+          <t>497608; 582053</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>474161; 660433</t>
+          <t>591241; 681880</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>909854; 1017516</t>
+          <t>911900; 1014316</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>895865; 1006541</t>
+          <t>892886; 1001909</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>825050; 934207</t>
+          <t>828218; 937146</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>835387; 1132870</t>
+          <t>963483; 1056030</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1415666; 1551048</t>
+          <t>1417405; 1552747</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1447600; 1588871</t>
+          <t>1441112; 1584220</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1351291; 1484295</t>
+          <t>1347838; 1480953</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1393293; 1744746</t>
+          <t>1583932; 1707610</t>
         </is>
       </c>
     </row>
